--- a/output/pdf_financials_xlsx/PHYS.U.xlsx
+++ b/output/pdf_financials_xlsx/PHYS.U.xlsx
@@ -1726,31 +1726,31 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>1e-05</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>5.862468</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>10.562922</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>25.598668</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>14.688442</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>6.147184</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.598317</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>3.065751</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>4.929218</v>
       </c>
     </row>
     <row r="35">
@@ -1794,31 +1794,31 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>1e-05</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>5.862468</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>10.562922</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>25.598668</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>14.688442</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>6.147184</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.598317</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>3.065751</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>4.929218</v>
       </c>
     </row>
     <row r="37">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -6424,7 +6424,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E21" s="5" t="n">
@@ -7381,7 +7381,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E38" s="5" t="n">

--- a/output/pdf_financials_xlsx/PHYS.U.xlsx
+++ b/output/pdf_financials_xlsx/PHYS.U.xlsx
@@ -10260,7 +10260,11 @@
           <t>Net cash generated by operating activities</t>
         </is>
       </c>
-      <c r="D87" t="inlineStr"/>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
       <c r="E87" t="inlineStr">
         <is>
           <t>-</t>
